--- a/results/pvdaq_34/report.xlsx
+++ b/results/pvdaq_34/report.xlsx
@@ -5381,9 +5381,7 @@
       <c r="J2" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="K2" s="6" t="n"/>
       <c r="L2" s="6" t="n"/>
     </row>
     <row r="3">
@@ -5418,7 +5416,7 @@
         <v>5463.716016957412</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>327.8229610174448</v>
+        <v>327.8229610174447</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>0</v>
